--- a/IMX425LLJ/РАСПИНОВКА_425.xlsx
+++ b/IMX425LLJ/РАСПИНОВКА_425.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20384"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4FF89F-5B96-4091-B00B-F9240E6C14A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3254D8BE-9478-4E6C-965B-BB8D9EDCA02B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="56">
   <si>
     <t>6581 A</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>XVS</t>
+  </si>
+  <si>
+    <t>IN</t>
   </si>
 </sst>
 </file>
@@ -246,13 +249,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -547,22 +550,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="4"/>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -571,7 +574,9 @@
       <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1" t="s">
         <v>2</v>
@@ -579,7 +584,9 @@
       <c r="F2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="5"/>
+      <c r="G2" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="1">
         <v>0</v>
@@ -669,10 +676,10 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="4"/>
+      <c r="J6" s="6"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -745,7 +752,9 @@
       <c r="B11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="1" t="s">
         <v>10</v>
@@ -753,10 +762,12 @@
       <c r="F11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="H11" s="3"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -850,8 +861,8 @@
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
@@ -897,7 +908,9 @@
       <c r="B20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="1" t="s">
         <v>18</v>
@@ -905,7 +918,9 @@
       <c r="F20" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1025,7 +1040,9 @@
       <c r="F29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G29" s="5"/>
+      <c r="G29" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -1060,18 +1077,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C20:C27"/>
+    <mergeCell ref="C2:C9"/>
+    <mergeCell ref="C11:C18"/>
+    <mergeCell ref="G2:G9"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="G29:G31"/>
     <mergeCell ref="G20:G27"/>
     <mergeCell ref="G11:G18"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C20:C27"/>
-    <mergeCell ref="C2:C9"/>
-    <mergeCell ref="C11:C18"/>
-    <mergeCell ref="G2:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
